--- a/report_temp.xlsx
+++ b/report_temp.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://accton365-my.sharepoint.com/personal/vicky_tseng_accton_com/Documents/Python/code/Excel_Vlookup_Python/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{8464A9CD-14F0-46D7-8063-23442CF46005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2700B83-7490-4BC9-A8BB-5CF1DACCD876}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{8464A9CD-14F0-46D7-8063-23442CF46005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{99C6131F-1897-FF45-A9BA-CAB3E5AA97B3}"/>
   <workbookProtection lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BA6135C1-322F-43F7-97FA-D2C8FB40AB51}"/>
@@ -24,7 +24,7 @@
   <definedNames>
     <definedName name="_Toc118790987" localSheetId="0">general!#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,6 +36,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -2175,6 +2177,9 @@
               <c:numCache>
                 <c:formatCode>0.0000_ </c:formatCode>
                 <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -2231,6 +2236,9 @@
               <c:numCache>
                 <c:formatCode>0.0000_ </c:formatCode>
                 <c:ptCount val="3"/>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -2287,6 +2295,9 @@
               <c:numCache>
                 <c:formatCode>0.0000_ </c:formatCode>
                 <c:ptCount val="3"/>
+                <c:pt idx="2">
+                  <c:v>9</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -2343,6 +2354,9 @@
               <c:numCache>
                 <c:formatCode>0.0000_ </c:formatCode>
                 <c:ptCount val="3"/>
+                <c:pt idx="1">
+                  <c:v>4</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -2399,6 +2413,9 @@
               <c:numCache>
                 <c:formatCode>0.0000_ </c:formatCode>
                 <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -4080,7 +4097,7 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>4.7619047619047616E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -4151,7 +4168,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>9.5238095238095233E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -4222,7 +4239,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>0.42857142857142855</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4287,7 +4304,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>0.19047619047619047</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -4352,7 +4369,7 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>0.23809523809523808</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -4687,7 +4704,7 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>4.7619047619047616E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4798,7 +4815,7 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>9.5238095238095233E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4909,7 +4926,7 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>0.42857142857142855</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5020,7 +5037,7 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>0.19047619047619047</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5131,7 +5148,7 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>0.23809523809523808</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7165,7 +7182,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="zh-TW"/>
+          <a:endParaRPr lang="en-US" altLang="zh-TW"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -15585,26 +15602,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E093B56-3128-43F6-835C-B82D2BA1C4C7}">
   <dimension ref="A1:BQ22"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="33.88671875" customWidth="1"/>
-    <col min="2" max="2" width="16.44140625" customWidth="1"/>
-    <col min="3" max="3" width="15.109375" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="10.21875" customWidth="1"/>
-    <col min="6" max="6" width="11.77734375" customWidth="1"/>
-    <col min="21" max="21" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="9" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="26" max="30" width="14.88671875" hidden="1" customWidth="1"/>
-    <col min="31" max="35" width="11.77734375" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="33.92578125" customWidth="1"/>
+    <col min="2" max="2" width="16.49609375" customWidth="1"/>
+    <col min="3" max="3" width="15.16796875" customWidth="1"/>
+    <col min="4" max="4" width="13.96875" customWidth="1"/>
+    <col min="5" max="5" width="10.2421875" customWidth="1"/>
+    <col min="6" max="6" width="11.83984375" customWidth="1"/>
+    <col min="21" max="21" width="12.23828125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.046875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="10.91015625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12.23828125" bestFit="1" customWidth="1"/>
+    <col min="26" max="30" width="14.8984375" hidden="1" customWidth="1"/>
+    <col min="31" max="35" width="11.83984375" hidden="1" customWidth="1"/>
     <col min="36" max="40" width="11.44140625" hidden="1" customWidth="1"/>
-    <col min="41" max="41" width="14.88671875" hidden="1" customWidth="1"/>
+    <col min="41" max="41" width="14.8984375" hidden="1" customWidth="1"/>
     <col min="42" max="69" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:69" ht="44.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:69" ht="44.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>16</v>
       </c>
@@ -15774,21 +15791,25 @@
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:69" ht="49.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:69" ht="36" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="22"/>
+      <c r="B2" s="22">
+        <v>1</v>
+      </c>
       <c r="C2" s="22"/>
       <c r="D2" s="22"/>
       <c r="E2" s="22"/>
-      <c r="F2" s="23"/>
+      <c r="F2" s="23">
+        <v>5</v>
+      </c>
       <c r="T2" s="41" t="s">
         <v>9</v>
       </c>
       <c r="U2" s="44">
         <f>表格2[[#This Row],[Raw Material]]</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V2" s="44">
         <f>B3</f>
@@ -15800,75 +15821,75 @@
       </c>
       <c r="X2" s="44">
         <f>SUM(U2:W2)</f>
-        <v>0</v>
-      </c>
-      <c r="Y2" s="42" t="e">
+        <v>1</v>
+      </c>
+      <c r="Y2" s="42">
         <f>表格9[[#Totals],[Raw Material]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z2" s="45" t="e">
+        <v>4.7619047619047616E-2</v>
+      </c>
+      <c r="Z2" s="45">
         <f>LARGE(C10:C14, 1)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA2" s="45" t="e">
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="AA2" s="45">
         <f>LARGE(C10:C14, 2)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB2" s="45" t="e">
+        <v>0.23809523809523808</v>
+      </c>
+      <c r="AB2" s="45">
         <f>LARGE(C10:C14, 3)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC2" s="45" t="e">
+        <v>0.19047619047619047</v>
+      </c>
+      <c r="AC2" s="45">
         <f>LARGE(C10:C14, 4)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD2" s="45" t="e">
+        <v>9.5238095238095233E-2</v>
+      </c>
+      <c r="AD2" s="45">
         <f>LARGE(C10:C14, 5)</f>
-        <v>#DIV/0!</v>
+        <v>4.7619047619047616E-2</v>
       </c>
       <c r="AE2" s="49">
         <f>LARGE($B$6:$F$6, 1)</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AF2" s="49">
         <f>LARGE($B$6:$F$6, 2)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AG2" s="49">
         <f>LARGE($B$6:$F$6, 3)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH2" s="49">
         <f>LARGE($B$6:$F$6, 4)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI2" s="49">
         <f>LARGE($B$6:$F$6, 5)</f>
-        <v>0</v>
-      </c>
-      <c r="AJ2" t="e">
+        <v>1</v>
+      </c>
+      <c r="AJ2" t="str">
         <f>INDEX($A$10:$A$14, MATCH(Z2, $C$10:$C$14, 0))</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AK2" t="e">
+        <v>運輸階段</v>
+      </c>
+      <c r="AK2" t="str">
         <f t="shared" ref="AK2:AN2" si="0">INDEX($A$10:$A$14, MATCH(AA2, $C$10:$C$14, 0))</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AL2" t="e">
+        <v>廢棄階段</v>
+      </c>
+      <c r="AL2" t="str">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AM2" t="e">
+        <v>使用階段</v>
+      </c>
+      <c r="AM2" t="str">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AN2" t="e">
+        <v>製程階段(含運輸)</v>
+      </c>
+      <c r="AN2" t="str">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+        <v>原料階段(含運輸)</v>
       </c>
       <c r="AO2" s="50">
         <f>表格2[[#This Row],[Raw Material]]</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP2" s="50">
         <f>B3</f>
@@ -15884,7 +15905,7 @@
       </c>
       <c r="AS2" s="50">
         <f>C3</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT2" s="50">
         <f>C4</f>
@@ -15900,7 +15921,7 @@
       </c>
       <c r="AW2" s="50">
         <f>D4</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AX2" s="50">
         <f>表格2[[#This Row],[Usage]]</f>
@@ -15908,7 +15929,7 @@
       </c>
       <c r="AY2" s="50">
         <f>E3</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AZ2" s="50">
         <f>E4</f>
@@ -15916,7 +15937,7 @@
       </c>
       <c r="BA2" s="50">
         <f>表格2[[#This Row],[Recycling]]</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BB2" s="50">
         <f>F3</f>
@@ -15928,69 +15949,73 @@
       </c>
       <c r="BD2" s="50">
         <f>B10</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE2" s="50">
         <f>B11</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF2" s="50">
         <f>B12</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BG2" s="50">
         <f>B13</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BH2" s="50">
         <f>B14</f>
-        <v>0</v>
-      </c>
-      <c r="BI2" s="50" t="e">
+        <v>5</v>
+      </c>
+      <c r="BI2" s="50">
         <f>C10</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BJ2" s="50" t="e">
+        <v>4.7619047619047616E-2</v>
+      </c>
+      <c r="BJ2" s="50">
         <f>C11</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BK2" s="50" t="e">
+        <v>9.5238095238095233E-2</v>
+      </c>
+      <c r="BK2" s="50">
         <f>C12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BL2" s="50" t="e">
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="BL2" s="50">
         <f>C13</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BM2" s="50" t="e">
+        <v>0.19047619047619047</v>
+      </c>
+      <c r="BM2" s="50">
         <f>C14</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BN2" s="51" t="e">
+        <v>0.23809523809523808</v>
+      </c>
+      <c r="BN2" s="51">
         <f>G19</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BO2" s="51" t="e">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="BO2" s="51">
         <f>G20</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BP2" s="51" t="e">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="BP2" s="51">
         <f>G21</f>
-        <v>#DIV/0!</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="BQ2" s="50">
         <f>B15</f>
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:69" ht="49.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:69" ht="36" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="22"/>
-      <c r="C3" s="22"/>
+      <c r="C3" s="22">
+        <v>2</v>
+      </c>
       <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
+      <c r="E3" s="22">
+        <v>4</v>
+      </c>
       <c r="F3" s="23"/>
       <c r="T3" s="41" t="s">
         <v>10</v>
@@ -16001,7 +16026,7 @@
       </c>
       <c r="V3" s="44">
         <f>表格2[[#This Row],[Manufacturing]]</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W3" s="44">
         <f>C4</f>
@@ -16009,20 +16034,22 @@
       </c>
       <c r="X3" s="44">
         <f t="shared" ref="X3:X6" si="1">SUM(U3:W3)</f>
-        <v>0</v>
-      </c>
-      <c r="Y3" s="42" t="e">
+        <v>2</v>
+      </c>
+      <c r="Y3" s="42">
         <f>表格9[[#Totals],[Manufacturing]]</f>
-        <v>#DIV/0!</v>
+        <v>9.5238095238095233E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:69" ht="33" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:69" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="24"/>
       <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
+      <c r="D4" s="24">
+        <v>9</v>
+      </c>
       <c r="E4" s="24"/>
       <c r="F4" s="25"/>
       <c r="T4" s="41" t="s">
@@ -16038,18 +16065,18 @@
       </c>
       <c r="W4" s="44">
         <f>表格2[[#This Row],[Distribution]]</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="X4" s="44">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y4" s="42" t="e">
+        <v>9</v>
+      </c>
+      <c r="Y4" s="42">
         <f>表格9[[#Totals],[Distribution]]</f>
-        <v>#DIV/0!</v>
+        <v>0.42857142857142855</v>
       </c>
     </row>
-    <row r="5" spans="1:69" ht="33" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:69" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="21"/>
       <c r="B5" s="25"/>
       <c r="C5" s="25"/>
@@ -16065,7 +16092,7 @@
       </c>
       <c r="V5" s="44">
         <f>E3</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W5" s="44">
         <f>E4</f>
@@ -16073,40 +16100,40 @@
       </c>
       <c r="X5" s="44">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y5" s="42" t="e">
+        <v>4</v>
+      </c>
+      <c r="Y5" s="42">
         <f>表格9[[#Totals],[Usage]]</f>
-        <v>#DIV/0!</v>
+        <v>0.19047619047619047</v>
       </c>
     </row>
-    <row r="6" spans="1:69" ht="33" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:69" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="26">
         <f>SUM(B2:B4)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6" s="26">
         <f t="shared" ref="C6:F6" si="2">SUM(C2:C4)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D6" s="26">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E6" s="26">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F6" s="26">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T6" s="41" t="s">
         <v>13</v>
       </c>
       <c r="U6" s="44">
         <f>F2</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V6" s="44">
         <f>F3</f>
@@ -16118,14 +16145,14 @@
       </c>
       <c r="X6" s="44">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y6" s="42" t="e">
+        <v>5</v>
+      </c>
+      <c r="Y6" s="42">
         <f>表格9[[#Totals],[Recycling]]</f>
-        <v>#DIV/0!</v>
+        <v>0.23809523809523808</v>
       </c>
     </row>
-    <row r="9" spans="1:69" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:69" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="19" t="s">
         <v>17</v>
       </c>
@@ -16136,85 +16163,85 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:69" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:69" ht="19.5" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="22">
         <f>B6</f>
-        <v>0</v>
-      </c>
-      <c r="C10" s="4" t="e">
+        <v>1</v>
+      </c>
+      <c r="C10" s="4">
         <f>B10/B$15</f>
-        <v>#DIV/0!</v>
+        <v>4.7619047619047616E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:69" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:69" ht="19.5" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>10</v>
       </c>
       <c r="B11" s="22">
         <f>C6</f>
-        <v>0</v>
-      </c>
-      <c r="C11" s="4" t="e">
+        <v>2</v>
+      </c>
+      <c r="C11" s="4">
         <f t="shared" ref="C11:C14" si="3">B11/B$15</f>
-        <v>#DIV/0!</v>
+        <v>9.5238095238095233E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:69" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:69" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="10" t="s">
         <v>11</v>
       </c>
       <c r="B12" s="22">
         <f>D6</f>
-        <v>0</v>
-      </c>
-      <c r="C12" s="4" t="e">
+        <v>9</v>
+      </c>
+      <c r="C12" s="4">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
+        <v>0.42857142857142855</v>
       </c>
     </row>
-    <row r="13" spans="1:69" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:69" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="10" t="s">
         <v>12</v>
       </c>
       <c r="B13" s="22">
         <f>E6</f>
-        <v>0</v>
-      </c>
-      <c r="C13" s="4" t="e">
+        <v>4</v>
+      </c>
+      <c r="C13" s="4">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
+        <v>0.19047619047619047</v>
       </c>
     </row>
-    <row r="14" spans="1:69" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:69" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
         <v>13</v>
       </c>
       <c r="B14" s="24">
         <f>F6</f>
-        <v>0</v>
-      </c>
-      <c r="C14" s="31" t="e">
+        <v>5</v>
+      </c>
+      <c r="C14" s="31">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
+        <v>0.23809523809523808</v>
       </c>
     </row>
-    <row r="15" spans="1:69" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:69" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="29" t="s">
         <v>20</v>
       </c>
       <c r="B15" s="30">
         <f>SUBTOTAL(109,B10:B14)</f>
-        <v>0</v>
-      </c>
-      <c r="C15" s="28" t="e">
+        <v>21</v>
+      </c>
+      <c r="C15" s="28">
         <f>B15/B$15</f>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="36.75" x14ac:dyDescent="0.15">
       <c r="A18" s="34" t="s">
         <v>19</v>
       </c>
@@ -16237,117 +16264,117 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A19" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="B19" s="27" t="e">
+      <c r="B19" s="27">
         <f>B2/SUM(表格2[[Raw Material]:[Recycling]])</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="C19" s="27" t="e">
+        <v>4.7619047619047616E-2</v>
+      </c>
+      <c r="C19" s="27">
         <f>C2/SUM(表格2[[Raw Material]:[Recycling]])</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D19" s="27" t="e">
+        <v>0</v>
+      </c>
+      <c r="D19" s="27">
         <f>D2/SUM(表格2[[Raw Material]:[Recycling]])</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E19" s="27" t="e">
+        <v>0</v>
+      </c>
+      <c r="E19" s="27">
         <f>E2/SUM(表格2[[Raw Material]:[Recycling]])</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F19" s="27" t="e">
+        <v>0</v>
+      </c>
+      <c r="F19" s="27">
         <f>F2/SUM(表格2[[Raw Material]:[Recycling]])</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G19" s="35" t="e">
+        <v>0.23809523809523808</v>
+      </c>
+      <c r="G19" s="35">
         <f>SUM(B19:F19)</f>
-        <v>#DIV/0!</v>
+        <v>0.2857142857142857</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A20" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="B20" s="27" t="e">
+      <c r="B20" s="27">
         <f>B3/SUM(表格2[[Raw Material]:[Recycling]])</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="C20" s="27" t="e">
+        <v>0</v>
+      </c>
+      <c r="C20" s="27">
         <f>C3/SUM(表格2[[Raw Material]:[Recycling]])</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D20" s="27" t="e">
+        <v>9.5238095238095233E-2</v>
+      </c>
+      <c r="D20" s="27">
         <f>D3/SUM(表格2[[Raw Material]:[Recycling]])</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E20" s="27" t="e">
+        <v>0</v>
+      </c>
+      <c r="E20" s="27">
         <f>E3/SUM(表格2[[Raw Material]:[Recycling]])</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F20" s="27" t="e">
+        <v>0.19047619047619047</v>
+      </c>
+      <c r="F20" s="27">
         <f>F3/SUM(表格2[[Raw Material]:[Recycling]])</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G20" s="35" t="e">
+        <v>0</v>
+      </c>
+      <c r="G20" s="35">
         <f t="shared" ref="G20:G21" si="4">SUM(B20:F20)</f>
-        <v>#DIV/0!</v>
+        <v>0.2857142857142857</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A21" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="27" t="e">
+      <c r="B21" s="27">
         <f>B4/SUM(表格2[[Raw Material]:[Recycling]])</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="C21" s="27" t="e">
+        <v>0</v>
+      </c>
+      <c r="C21" s="27">
         <f>C4/SUM(表格2[[Raw Material]:[Recycling]])</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D21" s="27" t="e">
+        <v>0</v>
+      </c>
+      <c r="D21" s="27">
         <f>D4/SUM(表格2[[Raw Material]:[Recycling]])</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E21" s="27" t="e">
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="E21" s="27">
         <f>E4/SUM(表格2[[Raw Material]:[Recycling]])</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F21" s="27" t="e">
+        <v>0</v>
+      </c>
+      <c r="F21" s="27">
         <f>F4/SUM(表格2[[Raw Material]:[Recycling]])</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G21" s="35" t="e">
+        <v>0</v>
+      </c>
+      <c r="G21" s="35">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>0.42857142857142855</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B22" s="27" t="e">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="B22" s="27">
         <f>SUM(B19:B21)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="C22" s="27" t="e">
+        <v>4.7619047619047616E-2</v>
+      </c>
+      <c r="C22" s="27">
         <f t="shared" ref="C22:F22" si="5">SUM(C19:C21)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D22" s="27" t="e">
+        <v>9.5238095238095233E-2</v>
+      </c>
+      <c r="D22" s="27">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E22" s="27" t="e">
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="E22" s="27">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F22" s="27" t="e">
+        <v>0.19047619047619047</v>
+      </c>
+      <c r="F22" s="27">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G22" s="36" t="e">
+        <v>0.23809523809523808</v>
+      </c>
+      <c r="G22" s="36">
         <f>SUM(B22:F22)</f>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -16366,14 +16393,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46306EB6-ACDE-4F68-9670-CCB46A7B9C54}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="32.109375" customWidth="1"/>
-    <col min="2" max="2" width="26.109375" customWidth="1"/>
-    <col min="3" max="3" width="24.21875" customWidth="1"/>
+    <col min="1" max="1" width="32.06640625" customWidth="1"/>
+    <col min="2" max="2" width="26.078125" customWidth="1"/>
+    <col min="3" max="3" width="24.21484375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
         <v>14</v>
       </c>
@@ -16384,52 +16411,52 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2"/>
       <c r="B2" s="1"/>
       <c r="C2" s="17"/>
     </row>
-    <row r="3" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2"/>
       <c r="B3" s="1"/>
       <c r="C3" s="17"/>
     </row>
-    <row r="4" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2"/>
       <c r="B4" s="1"/>
       <c r="C4" s="17"/>
     </row>
-    <row r="5" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2"/>
       <c r="B5" s="1"/>
       <c r="C5" s="17"/>
     </row>
-    <row r="6" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="1"/>
       <c r="C6" s="17"/>
     </row>
-    <row r="7" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2"/>
       <c r="B7" s="1"/>
       <c r="C7" s="17"/>
     </row>
-    <row r="8" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
       <c r="B8" s="1"/>
       <c r="C8" s="17"/>
     </row>
-    <row r="9" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
       <c r="B9" s="1"/>
       <c r="C9" s="17"/>
     </row>
-    <row r="10" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A10" s="18"/>
       <c r="B10" s="1"/>
       <c r="C10" s="17"/>
     </row>
-    <row r="11" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A11" s="16"/>
       <c r="B11" s="12"/>
       <c r="C11" s="17"/>
@@ -16447,14 +16474,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F02B6C0-7763-471E-9745-BCAF5F1D27EB}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="32.109375" customWidth="1"/>
-    <col min="2" max="2" width="26.109375" customWidth="1"/>
-    <col min="3" max="3" width="24.21875" customWidth="1"/>
+    <col min="1" max="1" width="32.06640625" customWidth="1"/>
+    <col min="2" max="2" width="26.078125" customWidth="1"/>
+    <col min="3" max="3" width="24.21484375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
         <v>14</v>
       </c>
@@ -16465,52 +16492,52 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A2" s="18"/>
       <c r="B2" s="1"/>
       <c r="C2" s="17"/>
     </row>
-    <row r="3" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2"/>
       <c r="B3" s="1"/>
       <c r="C3" s="17"/>
     </row>
-    <row r="4" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2"/>
       <c r="B4" s="1"/>
       <c r="C4" s="17"/>
     </row>
-    <row r="5" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2"/>
       <c r="B5" s="1"/>
       <c r="C5" s="17"/>
     </row>
-    <row r="6" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="1"/>
       <c r="C6" s="17"/>
     </row>
-    <row r="7" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2"/>
       <c r="B7" s="1"/>
       <c r="C7" s="17"/>
     </row>
-    <row r="8" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
       <c r="B8" s="1"/>
       <c r="C8" s="17"/>
     </row>
-    <row r="9" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
       <c r="B9" s="1"/>
       <c r="C9" s="17"/>
     </row>
-    <row r="10" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2"/>
       <c r="B10" s="1"/>
       <c r="C10" s="17"/>
     </row>
-    <row r="11" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A11" s="16"/>
       <c r="B11" s="12"/>
       <c r="C11" s="17"/>
@@ -16528,14 +16555,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AD4D200-CDD2-4280-A5ED-0B09BA172D64}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="32.109375" customWidth="1"/>
-    <col min="2" max="2" width="26.109375" customWidth="1"/>
-    <col min="3" max="3" width="24.21875" customWidth="1"/>
+    <col min="1" max="1" width="32.06640625" customWidth="1"/>
+    <col min="2" max="2" width="26.078125" customWidth="1"/>
+    <col min="3" max="3" width="24.21484375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
         <v>14</v>
       </c>
@@ -16546,52 +16573,52 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A2" s="18"/>
       <c r="B2" s="1"/>
       <c r="C2" s="17"/>
     </row>
-    <row r="3" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2"/>
       <c r="B3" s="1"/>
       <c r="C3" s="17"/>
     </row>
-    <row r="4" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2"/>
       <c r="B4" s="1"/>
       <c r="C4" s="17"/>
     </row>
-    <row r="5" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2"/>
       <c r="B5" s="1"/>
       <c r="C5" s="17"/>
     </row>
-    <row r="6" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="1"/>
       <c r="C6" s="17"/>
     </row>
-    <row r="7" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2"/>
       <c r="B7" s="1"/>
       <c r="C7" s="17"/>
     </row>
-    <row r="8" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
       <c r="B8" s="1"/>
       <c r="C8" s="17"/>
     </row>
-    <row r="9" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
       <c r="B9" s="1"/>
       <c r="C9" s="17"/>
     </row>
-    <row r="10" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2"/>
       <c r="B10" s="1"/>
       <c r="C10" s="17"/>
     </row>
-    <row r="11" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A11" s="16"/>
       <c r="B11" s="12"/>
       <c r="C11" s="17"/>
@@ -16609,14 +16636,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42ABAD01-A6AC-42A0-AA5A-637E28D77655}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="32.109375" customWidth="1"/>
-    <col min="2" max="2" width="26.109375" customWidth="1"/>
-    <col min="3" max="3" width="24.21875" customWidth="1"/>
+    <col min="1" max="1" width="32.06640625" customWidth="1"/>
+    <col min="2" max="2" width="26.078125" customWidth="1"/>
+    <col min="3" max="3" width="24.21484375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
         <v>14</v>
       </c>
@@ -16627,52 +16654,52 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A2" s="18"/>
       <c r="B2" s="1"/>
       <c r="C2" s="17"/>
     </row>
-    <row r="3" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2"/>
       <c r="B3" s="1"/>
       <c r="C3" s="17"/>
     </row>
-    <row r="4" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2"/>
       <c r="B4" s="1"/>
       <c r="C4" s="17"/>
     </row>
-    <row r="5" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2"/>
       <c r="B5" s="1"/>
       <c r="C5" s="17"/>
     </row>
-    <row r="6" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="1"/>
       <c r="C6" s="17"/>
     </row>
-    <row r="7" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2"/>
       <c r="B7" s="1"/>
       <c r="C7" s="17"/>
     </row>
-    <row r="8" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
       <c r="B8" s="1"/>
       <c r="C8" s="17"/>
     </row>
-    <row r="9" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
       <c r="B9" s="1"/>
       <c r="C9" s="17"/>
     </row>
-    <row r="10" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2"/>
       <c r="B10" s="1"/>
       <c r="C10" s="17"/>
     </row>
-    <row r="11" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A11" s="16"/>
       <c r="B11" s="12"/>
       <c r="C11" s="17"/>
@@ -16690,14 +16717,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF03671A-0463-422C-922B-8E823B302D42}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="32.109375" customWidth="1"/>
-    <col min="2" max="2" width="26.109375" customWidth="1"/>
-    <col min="3" max="3" width="24.21875" customWidth="1"/>
+    <col min="1" max="1" width="32.06640625" customWidth="1"/>
+    <col min="2" max="2" width="26.078125" customWidth="1"/>
+    <col min="3" max="3" width="24.21484375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
         <v>14</v>
       </c>
@@ -16708,52 +16735,52 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A2" s="18"/>
       <c r="B2" s="1"/>
       <c r="C2" s="17"/>
     </row>
-    <row r="3" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2"/>
       <c r="B3" s="1"/>
       <c r="C3" s="17"/>
     </row>
-    <row r="4" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2"/>
       <c r="B4" s="1"/>
       <c r="C4" s="17"/>
     </row>
-    <row r="5" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2"/>
       <c r="B5" s="1"/>
       <c r="C5" s="17"/>
     </row>
-    <row r="6" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="1"/>
       <c r="C6" s="17"/>
     </row>
-    <row r="7" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2"/>
       <c r="B7" s="1"/>
       <c r="C7" s="17"/>
     </row>
-    <row r="8" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
       <c r="B8" s="1"/>
       <c r="C8" s="17"/>
     </row>
-    <row r="9" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
       <c r="B9" s="1"/>
       <c r="C9" s="17"/>
     </row>
-    <row r="10" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2"/>
       <c r="B10" s="1"/>
       <c r="C10" s="17"/>
     </row>
-    <row r="11" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A11" s="16"/>
       <c r="B11" s="12"/>
       <c r="C11" s="17"/>
